--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-sg-total.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-sg-total.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -866,7 +866,7 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:code}
 </t>
   </si>
   <si>
@@ -1764,6 +1764,13 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="component:&amp;lt;slice&amp;gt;.code"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1882,6 +1889,10 @@
   </si>
   <si>
     <t>Observation.component.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>Observation.component:predicted.code.coding:sct</t>
@@ -12035,7 +12046,7 @@
         <v>81</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>81</v>
+        <v>557</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>81</v>
@@ -12093,7 +12104,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12104,10 +12115,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12219,10 +12230,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12336,10 +12347,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12455,10 +12466,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12484,13 +12495,13 @@
         <v>232</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>261</v>
@@ -12542,7 +12553,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>91</v>
@@ -12560,7 +12571,7 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>266</v>
@@ -12574,10 +12585,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12600,16 +12611,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>388</v>
@@ -12661,7 +12672,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12679,7 +12690,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>391</v>
@@ -12693,10 +12704,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12722,13 +12733,13 @@
         <v>232</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>437</v>
@@ -12780,7 +12791,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12812,10 +12823,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12841,10 +12852,10 @@
         <v>232</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>446</v>
@@ -12899,7 +12910,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12931,10 +12942,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12960,10 +12971,10 @@
         <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>497</v>
@@ -13018,7 +13029,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13050,13 +13061,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>552</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
@@ -13081,10 +13092,10 @@
         <v>494</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>555</v>
@@ -13160,7 +13171,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13171,10 +13182,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13286,10 +13297,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13403,10 +13414,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13522,10 +13533,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13551,13 +13562,13 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>261</v>
@@ -13609,7 +13620,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13627,7 +13638,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>266</v>
@@ -13641,10 +13652,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13756,10 +13767,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13873,10 +13884,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13948,7 +13959,7 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>272</v>
+        <v>597</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
@@ -13990,10 +14001,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>595</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>274</v>
@@ -14040,7 +14051,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14109,10 +14120,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>322</v>
@@ -14228,10 +14239,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14347,10 +14358,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14373,16 +14384,16 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>388</v>
@@ -14422,7 +14433,7 @@
         <v>81</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
@@ -14432,7 +14443,7 @@
         <v>117</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14450,7 +14461,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>391</v>
@@ -14464,13 +14475,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>81</v>
@@ -14495,13 +14506,13 @@
         <v>384</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>388</v>
@@ -14553,7 +14564,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14571,7 +14582,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>391</v>
@@ -14585,10 +14596,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14700,10 +14711,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14817,10 +14828,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14936,10 +14947,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15055,10 +15066,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15172,10 +15183,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15289,10 +15300,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15408,10 +15419,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15437,13 +15448,13 @@
         <v>232</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O111" t="s" s="2">
         <v>437</v>
@@ -15495,7 +15506,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15527,10 +15538,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15556,10 +15567,10 @@
         <v>232</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>446</v>
@@ -15614,7 +15625,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15646,10 +15657,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15675,10 +15686,10 @@
         <v>82</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>497</v>
@@ -15733,7 +15744,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15765,13 +15776,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>552</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>81</v>
@@ -15796,10 +15807,10 @@
         <v>494</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>555</v>
@@ -15875,7 +15886,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -15886,10 +15897,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16001,10 +16012,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16118,10 +16129,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16237,10 +16248,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16266,13 +16277,13 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>261</v>
@@ -16324,7 +16335,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>91</v>
@@ -16342,7 +16353,7 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>266</v>
@@ -16356,10 +16367,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16471,10 +16482,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16588,10 +16599,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16663,7 +16674,7 @@
         <v>81</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>272</v>
+        <v>597</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
@@ -16705,10 +16716,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>274</v>
@@ -16755,7 +16766,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -16824,10 +16835,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>322</v>
@@ -16943,10 +16954,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17062,10 +17073,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17088,16 +17099,16 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>388</v>
@@ -17137,7 +17148,7 @@
         <v>81</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
@@ -17147,7 +17158,7 @@
         <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17165,7 +17176,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>391</v>
@@ -17179,13 +17190,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>81</v>
@@ -17210,13 +17221,13 @@
         <v>384</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>388</v>
@@ -17268,7 +17279,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17286,7 +17297,7 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>391</v>
@@ -17300,10 +17311,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17415,10 +17426,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17532,10 +17543,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17651,10 +17662,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17770,10 +17781,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17816,7 +17827,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17887,10 +17898,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18004,10 +18015,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18052,7 +18063,7 @@
         <v>81</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>81</v>
@@ -18123,10 +18134,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18152,13 +18163,13 @@
         <v>232</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O134" t="s" s="2">
         <v>437</v>
@@ -18210,7 +18221,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18242,10 +18253,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18271,10 +18282,10 @@
         <v>232</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>446</v>
@@ -18329,7 +18340,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18361,10 +18372,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18390,10 +18401,10 @@
         <v>82</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>497</v>
@@ -18448,7 +18459,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18480,13 +18491,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>552</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>81</v>
@@ -18511,10 +18522,10 @@
         <v>494</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>555</v>
@@ -18590,7 +18601,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18601,10 +18612,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18716,10 +18727,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18833,10 +18844,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18952,10 +18963,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18981,13 +18992,13 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>261</v>
@@ -19039,7 +19050,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -19057,7 +19068,7 @@
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>266</v>
@@ -19071,10 +19082,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19186,10 +19197,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19303,10 +19314,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19378,7 +19389,7 @@
         <v>81</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>272</v>
+        <v>597</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -19420,10 +19431,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>274</v>
@@ -19470,7 +19481,7 @@
         <v>81</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>81</v>
@@ -19539,10 +19550,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19658,10 +19669,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19684,16 +19695,16 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>388</v>
@@ -19745,7 +19756,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19763,7 +19774,7 @@
         <v>81</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>391</v>
@@ -19777,10 +19788,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19806,13 +19817,13 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O148" t="s" s="2">
         <v>437</v>
@@ -19864,7 +19875,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19896,10 +19907,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19925,10 +19936,10 @@
         <v>232</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N149" t="s" s="2">
         <v>446</v>
@@ -19983,7 +19994,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20015,10 +20026,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20044,10 +20055,10 @@
         <v>82</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N150" t="s" s="2">
         <v>497</v>
@@ -20102,7 +20113,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-sg-total.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-sg-total.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5645" uniqueCount="668">
   <si>
     <t>Property</t>
   </si>
@@ -1318,7 +1318,7 @@
     <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
   </si>
   <si>
-    <t>/kPA*s</t>
+    <t>/(kPa.s)</t>
   </si>
   <si>
     <t>Quantity.unit</t>
@@ -1362,9 +1362,6 @@
   </si>
   <si>
     <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>/kPA.s</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -9696,46 +9693,46 @@
         <v>81</v>
       </c>
       <c r="S62" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9767,10 +9764,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9796,16 +9793,16 @@
         <v>232</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9833,11 +9830,11 @@
         <v>148</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9854,7 +9851,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9863,7 +9860,7 @@
         <v>91</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>103</v>
@@ -9875,7 +9872,7 @@
         <v>81</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9886,14 +9883,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9915,16 +9912,16 @@
         <v>232</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9952,11 +9949,11 @@
         <v>148</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z64" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>81</v>
       </c>
@@ -9973,7 +9970,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9991,24 +9988,24 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10031,19 +10028,19 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="N65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -10092,7 +10089,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10113,7 +10110,7 @@
         <v>81</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>81</v>
@@ -10124,10 +10121,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10153,13 +10150,13 @@
         <v>232</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10188,11 +10185,11 @@
         <v>156</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="Z66" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="AA66" t="s" s="2">
         <v>81</v>
       </c>
@@ -10209,7 +10206,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10227,24 +10224,24 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO66" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10270,16 +10267,16 @@
         <v>232</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10307,11 +10304,11 @@
         <v>156</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>475</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>81</v>
       </c>
@@ -10328,7 +10325,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10349,7 +10346,7 @@
         <v>81</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10360,10 +10357,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10386,16 +10383,16 @@
         <v>81</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10445,7 +10442,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10463,24 +10460,24 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO68" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10503,16 +10500,16 @@
         <v>81</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10562,7 +10559,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10580,24 +10577,24 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10620,19 +10617,19 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10681,7 +10678,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10693,16 +10690,16 @@
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
@@ -10713,10 +10710,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10828,10 +10825,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10945,14 +10942,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10974,10 +10971,10 @@
         <v>111</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>114</v>
@@ -11032,7 +11029,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -11064,10 +11061,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11090,13 +11087,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11147,7 +11144,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11156,7 +11153,7 @@
         <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>103</v>
@@ -11168,7 +11165,7 @@
         <v>81</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>81</v>
@@ -11179,10 +11176,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11205,13 +11202,13 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11262,7 +11259,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11271,7 +11268,7 @@
         <v>91</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>103</v>
@@ -11283,7 +11280,7 @@
         <v>81</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>81</v>
@@ -11294,10 +11291,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11323,16 +11320,16 @@
         <v>232</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>81</v>
@@ -11360,11 +11357,11 @@
         <v>170</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="Z76" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>523</v>
-      </c>
       <c r="AA76" t="s" s="2">
         <v>81</v>
       </c>
@@ -11381,7 +11378,7 @@
         <v>81</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11399,10 +11396,10 @@
         <v>81</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>81</v>
@@ -11413,10 +11410,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11442,16 +11439,16 @@
         <v>232</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N77" t="s" s="2">
+      <c r="O77" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>81</v>
@@ -11479,11 +11476,11 @@
         <v>156</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>81</v>
       </c>
@@ -11500,7 +11497,7 @@
         <v>81</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11518,10 +11515,10 @@
         <v>81</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AM77" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>81</v>
@@ -11532,10 +11529,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11558,17 +11555,17 @@
         <v>81</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>81</v>
@@ -11617,7 +11614,7 @@
         <v>81</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11649,10 +11646,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11678,10 +11675,10 @@
         <v>105</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11732,7 +11729,7 @@
         <v>81</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11753,7 +11750,7 @@
         <v>81</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>81</v>
@@ -11764,10 +11761,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11790,16 +11787,16 @@
         <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11849,7 +11846,7 @@
         <v>81</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11870,7 +11867,7 @@
         <v>81</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>81</v>
@@ -11881,10 +11878,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11907,16 +11904,16 @@
         <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11966,7 +11963,7 @@
         <v>81</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11987,7 +11984,7 @@
         <v>81</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>81</v>
@@ -11998,10 +11995,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12024,19 +12021,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>81</v>
@@ -12046,7 +12043,7 @@
         <v>81</v>
       </c>
       <c r="S82" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="T82" t="s" s="2">
         <v>81</v>
@@ -12083,7 +12080,7 @@
         <v>117</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12104,7 +12101,7 @@
         <v>81</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>81</v>
@@ -12115,10 +12112,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12230,10 +12227,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12347,14 +12344,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12376,10 +12373,10 @@
         <v>111</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>114</v>
@@ -12434,7 +12431,7 @@
         <v>81</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12466,10 +12463,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12495,13 +12492,13 @@
         <v>232</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O86" t="s" s="2">
         <v>261</v>
@@ -12553,7 +12550,7 @@
         <v>81</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>91</v>
@@ -12571,7 +12568,7 @@
         <v>81</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>266</v>
@@ -12585,10 +12582,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12611,16 +12608,16 @@
         <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>388</v>
@@ -12672,7 +12669,7 @@
         <v>81</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12690,7 +12687,7 @@
         <v>81</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>391</v>
@@ -12704,10 +12701,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12733,16 +12730,16 @@
         <v>232</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="N88" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="O88" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>81</v>
@@ -12770,11 +12767,11 @@
         <v>148</v>
       </c>
       <c r="Y88" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z88" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z88" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA88" t="s" s="2">
         <v>81</v>
       </c>
@@ -12791,7 +12788,7 @@
         <v>81</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12800,7 +12797,7 @@
         <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>103</v>
@@ -12812,7 +12809,7 @@
         <v>81</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>81</v>
@@ -12823,14 +12820,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12852,16 +12849,16 @@
         <v>232</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M89" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="N89" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O89" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>81</v>
@@ -12889,11 +12886,11 @@
         <v>148</v>
       </c>
       <c r="Y89" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z89" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z89" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA89" t="s" s="2">
         <v>81</v>
       </c>
@@ -12910,7 +12907,7 @@
         <v>81</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12928,24 +12925,24 @@
         <v>81</v>
       </c>
       <c r="AL89" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AM89" t="s" s="2">
+      <c r="AN89" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO89" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12971,16 +12968,16 @@
         <v>82</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M90" t="s" s="2">
-        <v>582</v>
-      </c>
       <c r="N90" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O90" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>81</v>
@@ -13029,7 +13026,7 @@
         <v>81</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -13050,7 +13047,7 @@
         <v>81</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>81</v>
@@ -13061,13 +13058,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C91" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C91" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>81</v>
@@ -13089,19 +13086,19 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>586</v>
-      </c>
       <c r="N91" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>81</v>
@@ -13150,7 +13147,7 @@
         <v>81</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13171,7 +13168,7 @@
         <v>81</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>81</v>
@@ -13182,10 +13179,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13297,10 +13294,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13414,14 +13411,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13443,10 +13440,10 @@
         <v>111</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>114</v>
@@ -13501,7 +13498,7 @@
         <v>81</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13533,10 +13530,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13562,13 +13559,13 @@
         <v>232</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O95" t="s" s="2">
         <v>261</v>
@@ -13620,7 +13617,7 @@
         <v>81</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>91</v>
@@ -13638,7 +13635,7 @@
         <v>81</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>266</v>
@@ -13652,10 +13649,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B96" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13767,10 +13764,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13884,10 +13881,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B98" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13959,7 +13956,7 @@
         <v>81</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AC98" s="2"/>
       <c r="AD98" t="s" s="2">
@@ -14001,10 +13998,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>274</v>
@@ -14051,7 +14048,7 @@
         <v>81</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>81</v>
@@ -14120,10 +14117,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>322</v>
@@ -14239,10 +14236,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14358,10 +14355,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14384,16 +14381,16 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O102" t="s" s="2">
         <v>388</v>
@@ -14433,7 +14430,7 @@
         <v>81</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
@@ -14443,7 +14440,7 @@
         <v>117</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14461,7 +14458,7 @@
         <v>81</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>391</v>
@@ -14475,13 +14472,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="C103" t="s" s="2">
         <v>605</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>606</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>81</v>
@@ -14506,13 +14503,13 @@
         <v>384</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O103" t="s" s="2">
         <v>388</v>
@@ -14564,7 +14561,7 @@
         <v>81</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14582,7 +14579,7 @@
         <v>81</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>391</v>
@@ -14596,10 +14593,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B104" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14711,10 +14708,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14828,10 +14825,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14947,10 +14944,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15066,10 +15063,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15112,7 +15109,7 @@
         <v>81</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>81</v>
@@ -15183,10 +15180,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15300,10 +15297,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>620</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15348,46 +15345,46 @@
         <v>81</v>
       </c>
       <c r="S110" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15419,10 +15416,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15448,16 +15445,16 @@
         <v>232</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M111" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="N111" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="N111" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="O111" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>81</v>
@@ -15485,11 +15482,11 @@
         <v>148</v>
       </c>
       <c r="Y111" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z111" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z111" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA111" t="s" s="2">
         <v>81</v>
       </c>
@@ -15506,7 +15503,7 @@
         <v>81</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15515,7 +15512,7 @@
         <v>91</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AJ111" t="s" s="2">
         <v>103</v>
@@ -15527,7 +15524,7 @@
         <v>81</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>81</v>
@@ -15538,14 +15535,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15567,16 +15564,16 @@
         <v>232</v>
       </c>
       <c r="L112" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M112" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M112" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="N112" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O112" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>81</v>
@@ -15604,11 +15601,11 @@
         <v>148</v>
       </c>
       <c r="Y112" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z112" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z112" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA112" t="s" s="2">
         <v>81</v>
       </c>
@@ -15625,7 +15622,7 @@
         <v>81</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15643,24 +15640,24 @@
         <v>81</v>
       </c>
       <c r="AL112" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AM112" t="s" s="2">
+      <c r="AN112" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO112" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15686,16 +15683,16 @@
         <v>82</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M113" t="s" s="2">
-        <v>582</v>
-      </c>
       <c r="N113" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O113" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>81</v>
@@ -15744,7 +15741,7 @@
         <v>81</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15765,7 +15762,7 @@
         <v>81</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>81</v>
@@ -15776,13 +15773,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C114" t="s" s="2">
         <v>624</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>625</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>81</v>
@@ -15804,19 +15801,19 @@
         <v>92</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="M114" t="s" s="2">
-        <v>627</v>
-      </c>
       <c r="N114" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O114" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>81</v>
@@ -15865,7 +15862,7 @@
         <v>81</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15886,7 +15883,7 @@
         <v>81</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>81</v>
@@ -15897,10 +15894,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16012,10 +16009,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16129,14 +16126,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16158,10 +16155,10 @@
         <v>111</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>114</v>
@@ -16216,7 +16213,7 @@
         <v>81</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -16248,10 +16245,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16277,13 +16274,13 @@
         <v>232</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M118" t="s" s="2">
+      <c r="N118" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O118" t="s" s="2">
         <v>261</v>
@@ -16335,7 +16332,7 @@
         <v>81</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>91</v>
@@ -16353,7 +16350,7 @@
         <v>81</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>266</v>
@@ -16367,10 +16364,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16482,10 +16479,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16599,10 +16596,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16674,7 +16671,7 @@
         <v>81</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AC121" s="2"/>
       <c r="AD121" t="s" s="2">
@@ -16716,10 +16713,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>274</v>
@@ -16766,7 +16763,7 @@
         <v>81</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>81</v>
@@ -16835,10 +16832,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>322</v>
@@ -16954,10 +16951,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17073,10 +17070,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17099,16 +17096,16 @@
         <v>92</v>
       </c>
       <c r="K125" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L125" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>388</v>
@@ -17148,7 +17145,7 @@
         <v>81</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
@@ -17158,7 +17155,7 @@
         <v>117</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17176,7 +17173,7 @@
         <v>81</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>391</v>
@@ -17190,13 +17187,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>81</v>
@@ -17221,13 +17218,13 @@
         <v>384</v>
       </c>
       <c r="L126" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M126" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M126" t="s" s="2">
+      <c r="N126" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>388</v>
@@ -17279,7 +17276,7 @@
         <v>81</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17297,7 +17294,7 @@
         <v>81</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>391</v>
@@ -17311,10 +17308,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17426,10 +17423,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17543,10 +17540,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17662,10 +17659,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17781,10 +17778,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17827,7 +17824,7 @@
         <v>81</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>81</v>
@@ -17898,10 +17895,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18015,10 +18012,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18063,7 +18060,7 @@
         <v>81</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>81</v>
@@ -18102,7 +18099,7 @@
         <v>81</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18134,10 +18131,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18163,16 +18160,16 @@
         <v>232</v>
       </c>
       <c r="L134" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="N134" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="O134" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>81</v>
@@ -18200,11 +18197,11 @@
         <v>148</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z134" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA134" t="s" s="2">
         <v>81</v>
       </c>
@@ -18221,7 +18218,7 @@
         <v>81</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18230,7 +18227,7 @@
         <v>91</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>103</v>
@@ -18242,7 +18239,7 @@
         <v>81</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>81</v>
@@ -18253,14 +18250,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -18282,16 +18279,16 @@
         <v>232</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M135" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="N135" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O135" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>81</v>
@@ -18319,11 +18316,11 @@
         <v>148</v>
       </c>
       <c r="Y135" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z135" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z135" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA135" t="s" s="2">
         <v>81</v>
       </c>
@@ -18340,7 +18337,7 @@
         <v>81</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18358,24 +18355,24 @@
         <v>81</v>
       </c>
       <c r="AL135" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM135" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AM135" t="s" s="2">
+      <c r="AN135" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO135" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18401,16 +18398,16 @@
         <v>82</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M136" t="s" s="2">
-        <v>582</v>
-      </c>
       <c r="N136" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O136" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>81</v>
@@ -18459,7 +18456,7 @@
         <v>81</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18480,7 +18477,7 @@
         <v>81</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>81</v>
@@ -18491,13 +18488,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="C137" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>81</v>
@@ -18519,19 +18516,19 @@
         <v>92</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="L137" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M137" t="s" s="2">
-        <v>654</v>
-      </c>
       <c r="N137" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="O137" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>81</v>
@@ -18580,7 +18577,7 @@
         <v>81</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18601,7 +18598,7 @@
         <v>81</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>81</v>
@@ -18612,10 +18609,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18727,10 +18724,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18844,14 +18841,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -18873,10 +18870,10 @@
         <v>111</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M140" t="s" s="2">
         <v>505</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>506</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>114</v>
@@ -18931,7 +18928,7 @@
         <v>81</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -18963,10 +18960,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18992,13 +18989,13 @@
         <v>232</v>
       </c>
       <c r="L141" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="M141" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>261</v>
@@ -19050,7 +19047,7 @@
         <v>81</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>91</v>
@@ -19068,7 +19065,7 @@
         <v>81</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>266</v>
@@ -19082,10 +19079,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19197,10 +19194,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19314,10 +19311,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19389,7 +19386,7 @@
         <v>81</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
@@ -19431,10 +19428,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>274</v>
@@ -19481,7 +19478,7 @@
         <v>81</v>
       </c>
       <c r="S145" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="T145" t="s" s="2">
         <v>81</v>
@@ -19550,10 +19547,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19669,10 +19666,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19695,16 +19692,16 @@
         <v>92</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="O147" t="s" s="2">
         <v>388</v>
@@ -19756,7 +19753,7 @@
         <v>81</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -19774,7 +19771,7 @@
         <v>81</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AM147" t="s" s="2">
         <v>391</v>
@@ -19788,10 +19785,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19817,16 +19814,16 @@
         <v>232</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M148" t="s" s="2">
+      <c r="N148" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="N148" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="O148" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>81</v>
@@ -19854,11 +19851,11 @@
         <v>148</v>
       </c>
       <c r="Y148" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="Z148" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="Z148" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AA148" t="s" s="2">
         <v>81</v>
       </c>
@@ -19875,7 +19872,7 @@
         <v>81</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -19884,7 +19881,7 @@
         <v>91</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>103</v>
@@ -19896,7 +19893,7 @@
         <v>81</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>81</v>
@@ -19907,14 +19904,14 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
@@ -19936,16 +19933,16 @@
         <v>232</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M149" t="s" s="2">
-        <v>579</v>
-      </c>
       <c r="N149" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O149" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>81</v>
@@ -19973,11 +19970,11 @@
         <v>148</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="Z149" t="s" s="2">
-        <v>449</v>
-      </c>
       <c r="AA149" t="s" s="2">
         <v>81</v>
       </c>
@@ -19994,7 +19991,7 @@
         <v>81</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20012,24 +20009,24 @@
         <v>81</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AM149" t="s" s="2">
+      <c r="AN149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO149" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AN149" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO149" t="s" s="2">
-        <v>452</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20055,16 +20052,16 @@
         <v>82</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M150" t="s" s="2">
-        <v>582</v>
-      </c>
       <c r="N150" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O150" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>81</v>
@@ -20113,7 +20110,7 @@
         <v>81</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20134,7 +20131,7 @@
         <v>81</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>81</v>
